--- a/salidas/empresas/PH.xlsx
+++ b/salidas/empresas/PH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>35.99570846557617</v>
+        <v>35.9957160949707</v>
       </c>
       <c r="C2" t="n">
         <v>50.51333236694336</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>37.24648666381836</v>
+        <v>37.24649047851562</v>
       </c>
       <c r="C3" t="n">
         <v>52.11333465576172</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>38.40909194946289</v>
+        <v>38.40908813476562</v>
       </c>
       <c r="C4" t="n">
         <v>53.7400016784668</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>38.61875152587891</v>
+        <v>38.61875915527344</v>
       </c>
       <c r="C5" t="n">
         <v>54.03333282470703</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>37.27932357788086</v>
+        <v>37.27933120727539</v>
       </c>
       <c r="C6" t="n">
         <v>52.01333236694336</v>
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.51753234863281</v>
+        <v>34.51753616333008</v>
       </c>
       <c r="C8" t="n">
         <v>48.15999984741211</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.50568389892578</v>
+        <v>35.50568008422852</v>
       </c>
       <c r="C9" t="n">
         <v>49.36666870117188</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>37.27018356323242</v>
+        <v>37.27018737792969</v>
       </c>
       <c r="C10" t="n">
         <v>51.81999969482422</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>40.09914398193359</v>
+        <v>40.09912490844727</v>
       </c>
       <c r="C11" t="n">
         <v>55.75333404541016</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>40.15095520019531</v>
+        <v>40.15095901489258</v>
       </c>
       <c r="C12" t="n">
         <v>55.6533317565918</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>36.97660446166992</v>
+        <v>36.97659683227539</v>
       </c>
       <c r="C13" t="n">
         <v>51.25333404541016</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>39.80468368530273</v>
+        <v>39.80467987060547</v>
       </c>
       <c r="C14" t="n">
         <v>55.17333221435547</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>41.64235305786133</v>
+        <v>41.64235687255859</v>
       </c>
       <c r="C16" t="n">
         <v>57.54000091552734</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>44.4551887512207</v>
+        <v>44.45518493652344</v>
       </c>
       <c r="C17" t="n">
         <v>61.42666625976562</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>49.03701782226562</v>
+        <v>49.03703689575195</v>
       </c>
       <c r="C18" t="n">
         <v>67.57333374023438</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>47.74045944213867</v>
+        <v>47.74047088623047</v>
       </c>
       <c r="C20" t="n">
         <v>65.78666687011719</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>52.15171051025391</v>
+        <v>52.15170288085938</v>
       </c>
       <c r="C21" t="n">
         <v>71.64666748046875</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>54.2674674987793</v>
+        <v>54.26744842529297</v>
       </c>
       <c r="C22" t="n">
         <v>74.55332946777344</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>58.50142288208008</v>
+        <v>58.50144577026367</v>
       </c>
       <c r="C23" t="n">
         <v>80.37000274658203</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>57.97002410888672</v>
+        <v>57.97005081176758</v>
       </c>
       <c r="C24" t="n">
         <v>79.43000030517578</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>54.9631462097168</v>
+        <v>54.963134765625</v>
       </c>
       <c r="C25" t="n">
         <v>75.30999755859375</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>50.71669769287109</v>
+        <v>50.7166862487793</v>
       </c>
       <c r="C28" t="n">
         <v>69.26999664306641</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>58.46293640136719</v>
+        <v>58.46296691894531</v>
       </c>
       <c r="C29" t="n">
         <v>79.84999847412109</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>62.14599990844727</v>
+        <v>62.14601516723633</v>
       </c>
       <c r="C30" t="n">
         <v>84.66999816894531</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>52.34738159179688</v>
+        <v>52.34737396240234</v>
       </c>
       <c r="C31" t="n">
         <v>71.31999969482422</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>45.2718391418457</v>
+        <v>45.27182388305664</v>
       </c>
       <c r="C32" t="n">
         <v>61.68000030517578</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>47.21604919433594</v>
+        <v>47.21604537963867</v>
       </c>
       <c r="C33" t="n">
         <v>64.06999969482422</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>39.05805969238281</v>
+        <v>39.05807495117188</v>
       </c>
       <c r="C34" t="n">
         <v>53</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>28.57133674621582</v>
+        <v>28.57135009765625</v>
       </c>
       <c r="C35" t="n">
         <v>38.77000045776367</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>30.49230575561523</v>
+        <v>30.49230194091797</v>
       </c>
       <c r="C36" t="n">
         <v>41.08000183105469</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>31.57602310180664</v>
+        <v>31.57601928710938</v>
       </c>
       <c r="C37" t="n">
         <v>42.54000091552734</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>28.36198616027832</v>
+        <v>28.36200141906738</v>
       </c>
       <c r="C38" t="n">
         <v>38.20999908447266</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>24.92255210876465</v>
+        <v>24.92256164550781</v>
       </c>
       <c r="C39" t="n">
         <v>33.36999893188477</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>25.37813377380371</v>
+        <v>25.37813568115234</v>
       </c>
       <c r="C40" t="n">
         <v>33.97999954223633</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>33.86987686157227</v>
+        <v>33.86988067626953</v>
       </c>
       <c r="C41" t="n">
         <v>45.34999847412109</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>31.7362003326416</v>
+        <v>31.73619842529297</v>
       </c>
       <c r="C42" t="n">
         <v>42.2599983215332</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>32.26188278198242</v>
+        <v>32.26188659667969</v>
       </c>
       <c r="C43" t="n">
         <v>42.95999908447266</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>33.2531623840332</v>
+        <v>33.253173828125</v>
       </c>
       <c r="C44" t="n">
         <v>44.27999877929688</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>36.73225402832031</v>
+        <v>36.73223495483398</v>
       </c>
       <c r="C45" t="n">
         <v>48.65999984741211</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>39.13275527954102</v>
+        <v>39.13276290893555</v>
       </c>
       <c r="C46" t="n">
         <v>51.84000015258789</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>39.97821426391602</v>
+        <v>39.97823333740234</v>
       </c>
       <c r="C47" t="n">
         <v>52.95999908447266</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>40.91264724731445</v>
+        <v>40.91268157958984</v>
       </c>
       <c r="C48" t="n">
         <v>53.95999908447266</v>
@@ -1381,11 +1393,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>40.85200500488281</v>
+        <v>40.85202026367188</v>
       </c>
       <c r="C49" t="n">
         <v>53.88000106811523</v>
@@ -1406,11 +1418,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>42.39117050170898</v>
+        <v>42.39115905761719</v>
       </c>
       <c r="C50" t="n">
         <v>55.90999984741211</v>
@@ -1431,11 +1443,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>45.93202209472656</v>
+        <v>45.93201446533203</v>
       </c>
       <c r="C51" t="n">
         <v>60.31000137329102</v>
@@ -1456,11 +1468,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>49.30588150024414</v>
+        <v>49.30591201782227</v>
       </c>
       <c r="C52" t="n">
         <v>64.73999786376953</v>
@@ -1481,11 +1493,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>52.68740081787109</v>
+        <v>52.68739318847656</v>
       </c>
       <c r="C53" t="n">
         <v>69.18000030517578</v>
@@ -1506,11 +1518,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>46.99220657348633</v>
+        <v>46.99221801757812</v>
       </c>
       <c r="C54" t="n">
         <v>61.45999908447266</v>
@@ -1531,11 +1543,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>42.40462112426758</v>
+        <v>42.40464782714844</v>
       </c>
       <c r="C55" t="n">
         <v>55.45999908447266</v>
@@ -1556,7 +1568,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1581,11 +1593,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>45.41981887817383</v>
+        <v>45.41983413696289</v>
       </c>
       <c r="C57" t="n">
         <v>59.15999984741211</v>
@@ -1610,11 +1622,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>53.78824615478516</v>
+        <v>53.78822708129883</v>
       </c>
       <c r="C58" t="n">
         <v>70.05999755859375</v>
@@ -1639,11 +1651,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>58.77090072631836</v>
+        <v>58.77093124389648</v>
       </c>
       <c r="C59" t="n">
         <v>76.55000305175781</v>
@@ -1668,11 +1680,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>61.81570434570312</v>
+        <v>61.81571578979492</v>
       </c>
       <c r="C60" t="n">
         <v>80.23000335693359</v>
@@ -1697,11 +1709,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>66.49250793457031</v>
+        <v>66.49251556396484</v>
       </c>
       <c r="C61" t="n">
         <v>86.30000305175781</v>
@@ -1726,7 +1738,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>68.95210266113281</v>
+        <v>68.95207214355469</v>
       </c>
       <c r="C63" t="n">
         <v>89.18000030517578</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>73.20458984375</v>
+        <v>73.20459747314453</v>
       </c>
       <c r="C64" t="n">
         <v>94.68000030517578</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>72.92620849609375</v>
+        <v>72.92623901367188</v>
       </c>
       <c r="C65" t="n">
         <v>94.31999969482422</v>
@@ -1842,7 +1854,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1871,7 +1883,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>61.351318359375</v>
+        <v>61.35130310058594</v>
       </c>
       <c r="C68" t="n">
         <v>79.01999664306641</v>
@@ -1929,7 +1941,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>49.28302764892578</v>
+        <v>49.28302383422852</v>
       </c>
       <c r="C70" t="n">
         <v>63.13000106811523</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>63.66275787353516</v>
+        <v>63.66273880004883</v>
       </c>
       <c r="C71" t="n">
         <v>81.55000305175781</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>64.91248321533203</v>
+        <v>64.91249084472656</v>
       </c>
       <c r="C72" t="n">
         <v>82.77999877929688</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>59.79195404052734</v>
+        <v>59.79194641113281</v>
       </c>
       <c r="C73" t="n">
         <v>76.25</v>
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>63.26575469970703</v>
+        <v>63.2657585144043</v>
       </c>
       <c r="C74" t="n">
         <v>80.68000030517578</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>70.73950958251953</v>
+        <v>70.739501953125</v>
       </c>
       <c r="C75" t="n">
         <v>89.80999755859375</v>
@@ -2132,7 +2144,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>69.0697021484375</v>
+        <v>69.06969451904297</v>
       </c>
       <c r="C77" t="n">
         <v>87.69000244140625</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>64.69622802734375</v>
+        <v>64.69625091552734</v>
       </c>
       <c r="C78" t="n">
         <v>81.73999786376953</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>60.84962844848633</v>
+        <v>60.84960174560547</v>
       </c>
       <c r="C79" t="n">
         <v>76.87999725341797</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>63.57230758666992</v>
+        <v>63.57234191894531</v>
       </c>
       <c r="C80" t="n">
         <v>80.31999969482422</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>63.62224960327148</v>
+        <v>63.62228012084961</v>
       </c>
       <c r="C81" t="n">
         <v>79.98000335693359</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>66.48599243164062</v>
+        <v>66.48602294921875</v>
       </c>
       <c r="C82" t="n">
         <v>83.58000183105469</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>62.57224655151367</v>
+        <v>62.57223129272461</v>
       </c>
       <c r="C83" t="n">
         <v>78.66000366210938</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>65.68332672119141</v>
+        <v>65.68334197998047</v>
       </c>
       <c r="C84" t="n">
         <v>82.15000152587891</v>
@@ -2393,7 +2405,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2422,7 +2434,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2451,7 +2463,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2480,7 +2492,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>71.14207458496094</v>
+        <v>71.14206695556641</v>
       </c>
       <c r="C89" t="n">
         <v>88.56999969482422</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>80.51924896240234</v>
+        <v>80.51924133300781</v>
       </c>
       <c r="C90" t="n">
         <v>99.76000213623047</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>77.00014495849609</v>
+        <v>77.00016021728516</v>
       </c>
       <c r="C91" t="n">
         <v>95.40000152587891</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>83.36031341552734</v>
+        <v>83.36032867431641</v>
       </c>
       <c r="C92" t="n">
         <v>103.2799987792969</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>81.02417755126953</v>
+        <v>81.02420043945312</v>
       </c>
       <c r="C93" t="n">
         <v>99.94999694824219</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>88.13356781005859</v>
+        <v>88.13358306884766</v>
       </c>
       <c r="C94" t="n">
         <v>108.7200012207031</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>94.61873626708984</v>
+        <v>94.61874389648438</v>
       </c>
       <c r="C95" t="n">
         <v>116.7200012207031</v>
@@ -2712,7 +2724,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>104.6880035400391</v>
+        <v>104.6879806518555</v>
       </c>
       <c r="C97" t="n">
         <v>128.6399993896484</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>92.26117706298828</v>
+        <v>92.26118469238281</v>
       </c>
       <c r="C98" t="n">
         <v>113.370002746582</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>98.52421569824219</v>
+        <v>98.52423858642578</v>
       </c>
       <c r="C99" t="n">
         <v>120.5500030517578</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>97.83769226074219</v>
+        <v>97.83769989013672</v>
       </c>
       <c r="C100" t="n">
         <v>119.7099990844727</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>103.6976699829102</v>
+        <v>103.6976623535156</v>
       </c>
       <c r="C101" t="n">
         <v>126.879997253418</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>102.7488098144531</v>
+        <v>102.7488250732422</v>
       </c>
       <c r="C102" t="n">
         <v>125.2300033569336</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>103.1590347290039</v>
+        <v>103.1590423583984</v>
       </c>
       <c r="C103" t="n">
         <v>125.7300033569336</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>94.31427764892578</v>
+        <v>94.31426239013672</v>
       </c>
       <c r="C104" t="n">
         <v>114.9499969482422</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>95.15585327148438</v>
+        <v>95.15584564208984</v>
       </c>
       <c r="C105" t="n">
         <v>115.5</v>
@@ -3002,7 +3014,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>104.6549530029297</v>
+        <v>104.6549606323242</v>
       </c>
       <c r="C107" t="n">
         <v>127.0299987792969</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>106.8293609619141</v>
+        <v>106.8293685913086</v>
       </c>
       <c r="C108" t="n">
         <v>129.0299987792969</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>106.7631301879883</v>
+        <v>106.7631683349609</v>
       </c>
       <c r="C109" t="n">
         <v>128.9499969482422</v>
@@ -3118,7 +3130,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>102.114860534668</v>
+        <v>102.1148681640625</v>
       </c>
       <c r="C111" t="n">
         <v>122.6900024414062</v>
@@ -3176,7 +3188,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>99.34329986572266</v>
+        <v>99.34331512451172</v>
       </c>
       <c r="C113" t="n">
         <v>119.3600006103516</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>100.7532196044922</v>
+        <v>100.7532043457031</v>
       </c>
       <c r="C114" t="n">
         <v>120.4300003051758</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>97.32309722900391</v>
+        <v>97.3231201171875</v>
       </c>
       <c r="C115" t="n">
         <v>116.3300018310547</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>94.32801055908203</v>
+        <v>94.32803344726562</v>
       </c>
       <c r="C116" t="n">
         <v>112.75</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>90.63832092285156</v>
+        <v>90.6383056640625</v>
       </c>
       <c r="C117" t="n">
         <v>107.6600036621094</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>81.91629791259766</v>
+        <v>81.91627502441406</v>
       </c>
       <c r="C118" t="n">
         <v>97.30000305175781</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>88.14630889892578</v>
+        <v>88.14630126953125</v>
       </c>
       <c r="C119" t="n">
         <v>104.6999969482422</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>88.63850402832031</v>
+        <v>88.63848876953125</v>
       </c>
       <c r="C120" t="n">
         <v>104.6600036621094</v>
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>82.13416290283203</v>
+        <v>82.13417053222656</v>
       </c>
       <c r="C121" t="n">
         <v>96.98000335693359</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>82.28659820556641</v>
+        <v>82.28660583496094</v>
       </c>
       <c r="C122" t="n">
         <v>97.16000366210938</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>86.24341583251953</v>
+        <v>86.243408203125</v>
       </c>
       <c r="C123" t="n">
         <v>101.1999969482422</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>94.66323852539062</v>
+        <v>94.66324615478516</v>
       </c>
       <c r="C124" t="n">
         <v>111.0800018310547</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>98.87311553955078</v>
+        <v>98.87315368652344</v>
       </c>
       <c r="C125" t="n">
         <v>116.0199966430664</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>98.42140197753906</v>
+        <v>98.42137145996094</v>
       </c>
       <c r="C126" t="n">
         <v>114.8399963378906</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>92.60214233398438</v>
+        <v>92.60212707519531</v>
       </c>
       <c r="C127" t="n">
         <v>108.0500030517578</v>
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>97.86432647705078</v>
+        <v>97.86433410644531</v>
       </c>
       <c r="C128" t="n">
         <v>114.1900024414062</v>
@@ -3669,7 +3681,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3698,7 +3710,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>105.7406692504883</v>
+        <v>105.7406997680664</v>
       </c>
       <c r="C131" t="n">
         <v>122.75</v>
@@ -3756,7 +3768,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>121.208122253418</v>
+        <v>121.2080917358398</v>
       </c>
       <c r="C133" t="n">
         <v>140</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>127.381103515625</v>
+        <v>127.3810882568359</v>
       </c>
       <c r="C134" t="n">
         <v>147.1300048828125</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>134.6567840576172</v>
+        <v>134.6567687988281</v>
       </c>
       <c r="C135" t="n">
         <v>154.8399963378906</v>
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>139.4224853515625</v>
+        <v>139.4224700927734</v>
       </c>
       <c r="C136" t="n">
         <v>160.3200073242188</v>
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>139.8398742675781</v>
+        <v>139.8399047851562</v>
       </c>
       <c r="C137" t="n">
         <v>160.8000030517578</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>137.5140533447266</v>
+        <v>137.5140686035156</v>
       </c>
       <c r="C138" t="n">
         <v>157.4700012207031</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>139.5663146972656</v>
+        <v>139.5662384033203</v>
       </c>
       <c r="C139" t="n">
         <v>159.8200073242188</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>144.9456176757812</v>
+        <v>144.9456024169922</v>
       </c>
       <c r="C140" t="n">
         <v>165.9799957275391</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>141.0916137695312</v>
+        <v>141.0916290283203</v>
       </c>
       <c r="C141" t="n">
         <v>160.8899993896484</v>
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>153.4829254150391</v>
+        <v>153.48291015625</v>
       </c>
       <c r="C142" t="n">
         <v>175.0200042724609</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>160.138916015625</v>
+        <v>160.1389007568359</v>
       </c>
       <c r="C143" t="n">
         <v>182.6100006103516</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>165.0075378417969</v>
+        <v>165.0075225830078</v>
       </c>
       <c r="C144" t="n">
         <v>187.4900054931641</v>
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>175.6477355957031</v>
+        <v>175.6477813720703</v>
       </c>
       <c r="C145" t="n">
         <v>199.5800018310547</v>
@@ -4162,11 +4174,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>177.2670593261719</v>
+        <v>177.26708984375</v>
       </c>
       <c r="C146" t="n">
         <v>201.4199981689453</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>157.6366729736328</v>
+        <v>157.6367034912109</v>
       </c>
       <c r="C147" t="n">
         <v>178.4700012207031</v>
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>151.065185546875</v>
+        <v>151.0651702880859</v>
       </c>
       <c r="C148" t="n">
         <v>171.0299987792969</v>
@@ -4249,7 +4261,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4278,7 +4290,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>138.2713165283203</v>
+        <v>138.2713012695312</v>
       </c>
       <c r="C151" t="n">
         <v>155.8500061035156</v>
@@ -4336,7 +4348,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4365,7 +4377,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4394,7 +4406,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>135.1260375976562</v>
+        <v>135.1259918212891</v>
       </c>
       <c r="C155" t="n">
         <v>151.6300048828125</v>
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>153.9988250732422</v>
+        <v>153.9987945556641</v>
       </c>
       <c r="C156" t="n">
         <v>172.0399932861328</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>133.5002746582031</v>
+        <v>133.5002288818359</v>
       </c>
       <c r="C157" t="n">
         <v>149.1399993896484</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>147.5269775390625</v>
+        <v>147.5269927978516</v>
       </c>
       <c r="C158" t="n">
         <v>164.8099975585938</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>158.4120483398438</v>
+        <v>158.4119873046875</v>
       </c>
       <c r="C159" t="n">
         <v>176.1600036621094</v>
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>154.3294219970703</v>
+        <v>154.3294067382812</v>
       </c>
       <c r="C160" t="n">
         <v>171.6199951171875</v>
@@ -4597,11 +4609,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>162.8363342285156</v>
+        <v>162.8363647460938</v>
       </c>
       <c r="C161" t="n">
         <v>181.0800018310547</v>
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>137.6785278320312</v>
+        <v>137.6784820556641</v>
       </c>
       <c r="C162" t="n">
         <v>152.3200073242188</v>
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>153.6680755615234</v>
+        <v>153.6680908203125</v>
       </c>
       <c r="C163" t="n">
         <v>170.0099945068359</v>
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>158.2507019042969</v>
+        <v>158.250732421875</v>
       </c>
       <c r="C164" t="n">
         <v>175.0800018310547</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>150.6718597412109</v>
+        <v>150.6719055175781</v>
       </c>
       <c r="C165" t="n">
         <v>165.7700042724609</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>164.1602325439453</v>
+        <v>164.1602478027344</v>
       </c>
       <c r="C166" t="n">
         <v>180.6100006103516</v>
@@ -4771,7 +4783,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4800,7 +4812,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>187.9043579101562</v>
+        <v>187.9043731689453</v>
       </c>
       <c r="C169" t="n">
         <v>205.8200073242188</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>178.6561584472656</v>
+        <v>178.6560821533203</v>
       </c>
       <c r="C170" t="n">
         <v>195.6900024414062</v>
@@ -4887,11 +4899,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>169.3950347900391</v>
+        <v>169.39501953125</v>
       </c>
       <c r="C171" t="n">
         <v>184.7700042724609</v>
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>118.9349899291992</v>
+        <v>118.9349517822266</v>
       </c>
       <c r="C172" t="n">
         <v>129.7299957275391</v>
@@ -4945,11 +4957,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>144.9626312255859</v>
+        <v>144.9625854492188</v>
       </c>
       <c r="C173" t="n">
         <v>158.1199951171875</v>
@@ -4974,11 +4986,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>165.9466857910156</v>
+        <v>165.9466400146484</v>
       </c>
       <c r="C174" t="n">
         <v>179.9700012207031</v>
@@ -5003,11 +5015,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>168.9895172119141</v>
+        <v>168.9895629882812</v>
       </c>
       <c r="C175" t="n">
         <v>183.2700042724609</v>
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>164.9784851074219</v>
+        <v>164.9784698486328</v>
       </c>
       <c r="C176" t="n">
         <v>178.9199981689453</v>
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>190.7578277587891</v>
+        <v>190.7578735351562</v>
       </c>
       <c r="C177" t="n">
         <v>206.0099945068359</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>187.3595428466797</v>
+        <v>187.3595123291016</v>
       </c>
       <c r="C178" t="n">
         <v>202.3399963378906</v>
@@ -5119,11 +5131,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>192.9338684082031</v>
+        <v>192.933837890625</v>
       </c>
       <c r="C179" t="n">
         <v>208.3600006103516</v>
@@ -5148,11 +5160,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>248.4764251708984</v>
+        <v>248.4764099121094</v>
       </c>
       <c r="C180" t="n">
         <v>267.260009765625</v>
@@ -5177,7 +5189,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5206,7 +5218,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>267.6370849609375</v>
+        <v>267.6371154785156</v>
       </c>
       <c r="C183" t="n">
         <v>286.9599914550781</v>
@@ -5264,11 +5276,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>294.1900329589844</v>
+        <v>294.1901245117188</v>
       </c>
       <c r="C184" t="n">
         <v>315.4299926757812</v>
@@ -5293,7 +5305,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5322,11 +5334,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>288.3409423828125</v>
+        <v>288.3409729003906</v>
       </c>
       <c r="C186" t="n">
         <v>308.1499938964844</v>
@@ -5351,11 +5363,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>287.3678588867188</v>
+        <v>287.3677062988281</v>
       </c>
       <c r="C187" t="n">
         <v>307.1099853515625</v>
@@ -5380,7 +5392,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5409,11 +5421,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>278.5442504882812</v>
+        <v>278.5442199707031</v>
       </c>
       <c r="C189" t="n">
         <v>296.6700134277344</v>
@@ -5438,11 +5450,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>262.5359191894531</v>
+        <v>262.5358581542969</v>
       </c>
       <c r="C190" t="n">
         <v>279.6199951171875</v>
@@ -5467,7 +5479,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5496,7 +5508,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5525,11 +5537,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>299.6200561523438</v>
+        <v>299.6201477050781</v>
       </c>
       <c r="C193" t="n">
         <v>318.1199951171875</v>
@@ -5554,11 +5566,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>291.9817199707031</v>
+        <v>291.9816589355469</v>
       </c>
       <c r="C194" t="n">
         <v>310.010009765625</v>
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>280.0718078613281</v>
+        <v>280.0717163085938</v>
       </c>
       <c r="C195" t="n">
         <v>296.3900146484375</v>
@@ -5612,7 +5624,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5641,11 +5653,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>255.9096374511719</v>
+        <v>255.9095764160156</v>
       </c>
       <c r="C197" t="n">
         <v>270.8200073242188</v>
@@ -5670,11 +5682,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>258.4831237792969</v>
+        <v>258.4830627441406</v>
       </c>
       <c r="C198" t="n">
         <v>272.1700134277344</v>
@@ -5699,7 +5711,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5728,11 +5740,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>274.5521545410156</v>
+        <v>274.5521850585938</v>
       </c>
       <c r="C200" t="n">
         <v>289.0899963378906</v>
@@ -5757,11 +5769,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>252.8237457275391</v>
+        <v>252.8237152099609</v>
       </c>
       <c r="C201" t="n">
         <v>265</v>
@@ -5786,11 +5798,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>231.1762847900391</v>
+        <v>231.17626953125</v>
       </c>
       <c r="C202" t="n">
         <v>242.3099975585938</v>
@@ -5815,11 +5827,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>277.2665405273438</v>
+        <v>277.2664794921875</v>
       </c>
       <c r="C203" t="n">
         <v>290.6199951171875</v>
@@ -5844,11 +5856,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>286.5218200683594</v>
+        <v>286.5217590332031</v>
       </c>
       <c r="C204" t="n">
         <v>298.9400024414062</v>
@@ -5873,7 +5885,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5902,11 +5914,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>312.4577026367188</v>
+        <v>312.4576721191406</v>
       </c>
       <c r="C206" t="n">
         <v>326</v>
@@ -5931,11 +5943,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>338.512939453125</v>
+        <v>338.5130004882812</v>
       </c>
       <c r="C207" t="n">
         <v>351.8500061035156</v>
@@ -5960,7 +5972,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5989,11 +6001,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>312.5652160644531</v>
+        <v>312.5652465820312</v>
       </c>
       <c r="C209" t="n">
         <v>324.8800048828125</v>
@@ -6018,11 +6030,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>309.69580078125</v>
+        <v>309.6956481933594</v>
       </c>
       <c r="C210" t="n">
         <v>320.4400024414062</v>
@@ -6047,7 +6059,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6076,11 +6088,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>396.2624816894531</v>
+        <v>396.2625122070312</v>
       </c>
       <c r="C212" t="n">
         <v>410.010009765625</v>
@@ -6105,11 +6117,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>404.4241027832031</v>
+        <v>404.424072265625</v>
       </c>
       <c r="C213" t="n">
         <v>416.8999938964844</v>
@@ -6134,11 +6146,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>377.8634033203125</v>
+        <v>377.8634948730469</v>
       </c>
       <c r="C214" t="n">
         <v>389.5199890136719</v>
@@ -6163,11 +6175,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>357.8701782226562</v>
+        <v>357.8702087402344</v>
       </c>
       <c r="C215" t="n">
         <v>368.9100036621094</v>
@@ -6192,11 +6204,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>421.7287902832031</v>
+        <v>421.7288208007812</v>
       </c>
       <c r="C216" t="n">
         <v>433.1799926757812</v>
@@ -6221,7 +6233,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6250,11 +6262,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>452.220947265625</v>
+        <v>452.2208557128906</v>
       </c>
       <c r="C218" t="n">
         <v>464.5</v>
@@ -6279,11 +6291,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>522.8001098632812</v>
+        <v>522.7999877929688</v>
       </c>
       <c r="C219" t="n">
         <v>535.4500122070312</v>
@@ -6308,11 +6320,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>542.6594848632812</v>
+        <v>542.659423828125</v>
       </c>
       <c r="C220" t="n">
         <v>555.7899780273438</v>
@@ -6337,7 +6349,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6366,11 +6378,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>520.4917602539062</v>
+        <v>520.49169921875</v>
       </c>
       <c r="C222" t="n">
         <v>531.52001953125</v>
@@ -6395,11 +6407,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>495.3152160644531</v>
+        <v>495.315185546875</v>
       </c>
       <c r="C223" t="n">
         <v>505.8099975585938</v>
@@ -6424,7 +6436,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6453,11 +6465,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>589.374755859375</v>
+        <v>589.3748168945312</v>
       </c>
       <c r="C225" t="n">
         <v>600.2000122070312</v>
@@ -6482,11 +6494,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>620.424560546875</v>
+        <v>620.4244995117188</v>
       </c>
       <c r="C226" t="n">
         <v>631.8200073242188</v>
@@ -6511,11 +6523,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>622.6339721679688</v>
+        <v>622.6339111328125</v>
       </c>
       <c r="C227" t="n">
         <v>634.0700073242188</v>
@@ -6540,11 +6552,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>691.8574829101562</v>
+        <v>691.857421875</v>
       </c>
       <c r="C228" t="n">
         <v>702.9000244140625</v>
@@ -6569,11 +6581,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>626.0379638671875</v>
+        <v>626.0379028320312</v>
       </c>
       <c r="C229" t="n">
         <v>636.030029296875</v>
@@ -6598,11 +6610,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>695.9422607421875</v>
+        <v>695.9421997070312</v>
       </c>
       <c r="C230" t="n">
         <v>707.0499877929688</v>
@@ -6627,7 +6639,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6656,11 +6668,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>599.7140502929688</v>
+        <v>599.714111328125</v>
       </c>
       <c r="C232" t="n">
         <v>607.8499755859375</v>
@@ -6685,11 +6697,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>596.96142578125</v>
+        <v>596.9613037109375</v>
       </c>
       <c r="C233" t="n">
         <v>605.0599975585938</v>
@@ -6714,7 +6726,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6743,11 +6755,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>691.0602416992188</v>
+        <v>691.0601806640625</v>
       </c>
       <c r="C235" t="n">
         <v>698.469970703125</v>
@@ -6772,11 +6784,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>724.1355590820312</v>
+        <v>724.1356811523438</v>
       </c>
       <c r="C236" t="n">
         <v>731.9000244140625</v>
@@ -6801,11 +6813,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>751.2943725585938</v>
+        <v>751.2943115234375</v>
       </c>
       <c r="C237" t="n">
         <v>759.3499755859375</v>
@@ -6830,7 +6842,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6859,7 +6871,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6888,7 +6900,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6917,7 +6929,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6946,7 +6958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6975,7 +6987,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,7 +7045,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>971.2100219726562</v>
+        <v>974.97998046875</v>
       </c>
       <c r="C250" t="n">
-        <v>971.2100219726562</v>
+        <v>974.97998046875</v>
       </c>
       <c r="D250" t="n">
-        <v>9630400</v>
+        <v>10182700</v>
       </c>
       <c r="E250" t="n">
         <v>28.48</v>
       </c>
       <c r="F250" t="n">
-        <v>34.10147549061293</v>
+        <v>34.23384762881847</v>
       </c>
       <c r="G250" t="n">
         <v>126047469</v>
       </c>
       <c r="H250" t="n">
-        <v>122418565137.0877</v>
+        <v>122893758863.7554</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07640296212532439</v>
+        <v>0.08078464471190612</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40213</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7456,7 +7468,7 @@
       <c r="I5" t="n">
         <v>3.1</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="K5" t="n">
@@ -7469,13 +7481,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7502,7 +7514,7 @@
       <c r="I6" t="n">
         <v>2.05</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="K6" t="n">
@@ -7515,13 +7527,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40213</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7548,7 +7560,7 @@
       <c r="I7" t="n">
         <v>1.73</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="K7" t="n">
@@ -7561,13 +7573,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7594,7 +7606,7 @@
       <c r="I8" t="n">
         <v>2.34</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="K8" t="n">
@@ -7607,13 +7619,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7640,7 +7652,7 @@
       <c r="I9" t="n">
         <v>3.38</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="K9" t="n">
@@ -7653,13 +7665,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7686,7 +7698,7 @@
       <c r="I10" t="n">
         <v>4.44</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="K10" t="n">
@@ -7699,13 +7711,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40582</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7732,7 +7744,7 @@
       <c r="I11" t="n">
         <v>5.19</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40582</v>
       </c>
       <c r="K11" t="n">
@@ -7745,13 +7757,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7778,7 +7790,7 @@
       <c r="I12" t="n">
         <v>5.930000000000001</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="K12" t="n">
@@ -7791,13 +7803,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40781</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7824,7 +7836,7 @@
       <c r="I13" t="n">
         <v>6.37</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40781</v>
       </c>
       <c r="K13" t="n">
@@ -7837,13 +7849,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7870,7 +7882,7 @@
       <c r="I14" t="n">
         <v>6.77</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="K14" t="n">
@@ -7883,13 +7895,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40947</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7916,7 +7928,7 @@
       <c r="I15" t="n">
         <v>6.94</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40947</v>
       </c>
       <c r="K15" t="n">
@@ -7929,13 +7941,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7962,7 +7974,7 @@
       <c r="I16" t="n">
         <v>7.27</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="K16" t="n">
@@ -7975,13 +7987,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41145</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8008,7 +8020,7 @@
       <c r="I17" t="n">
         <v>7.44</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41145</v>
       </c>
       <c r="K17" t="n">
@@ -8021,13 +8033,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8054,7 +8066,7 @@
       <c r="I18" t="n">
         <v>7.1</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K18" t="n">
@@ -8067,13 +8079,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41311</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8100,7 +8112,7 @@
       <c r="I19" t="n">
         <v>6.73</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41311</v>
       </c>
       <c r="K19" t="n">
@@ -8113,13 +8125,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8146,7 +8158,7 @@
       <c r="I20" t="n">
         <v>6.4</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="K20" t="n">
@@ -8159,13 +8171,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41515</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8192,7 +8204,7 @@
       <c r="I21" t="n">
         <v>6.22</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41515</v>
       </c>
       <c r="K21" t="n">
@@ -8205,13 +8217,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8238,7 +8250,7 @@
       <c r="I22" t="n">
         <v>6.26</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="K22" t="n">
@@ -8251,13 +8263,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8284,7 +8296,7 @@
       <c r="I23" t="n">
         <v>6.73</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="K23" t="n">
@@ -8297,13 +8309,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8330,7 +8342,7 @@
       <c r="I24" t="n">
         <v>6.65</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="K24" t="n">
@@ -8343,13 +8355,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41873</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8376,7 +8388,7 @@
       <c r="I25" t="n">
         <v>6.850000000000001</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41873</v>
       </c>
       <c r="K25" t="n">
@@ -8389,13 +8401,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8422,7 +8434,7 @@
       <c r="I26" t="n">
         <v>7.09</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="K26" t="n">
@@ -8435,13 +8447,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8468,7 +8480,7 @@
       <c r="I27" t="n">
         <v>7.23</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="K27" t="n">
@@ -8481,13 +8493,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8514,7 +8526,7 @@
       <c r="I28" t="n">
         <v>7.65</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="K28" t="n">
@@ -8527,13 +8539,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42242</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8560,7 +8572,7 @@
       <c r="I29" t="n">
         <v>6.94</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42242</v>
       </c>
       <c r="K29" t="n">
@@ -8573,13 +8585,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8606,7 +8618,7 @@
       <c r="I30" t="n">
         <v>6.5</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="K30" t="n">
@@ -8619,13 +8631,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8652,7 +8664,7 @@
       <c r="I31" t="n">
         <v>6.029999999999999</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="K31" t="n">
@@ -8665,13 +8677,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8698,7 +8710,7 @@
       <c r="I32" t="n">
         <v>5.38</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K32" t="n">
@@ -8711,13 +8723,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42608</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8744,7 +8756,7 @@
       <c r="I33" t="n">
         <v>5.88</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42608</v>
       </c>
       <c r="K33" t="n">
@@ -8757,13 +8769,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8790,7 +8802,7 @@
       <c r="I34" t="n">
         <v>6.02</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="K34" t="n">
@@ -8803,13 +8815,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8836,7 +8848,7 @@
       <c r="I35" t="n">
         <v>6.470000000000001</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="K35" t="n">
@@ -8849,13 +8861,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8882,7 +8894,7 @@
       <c r="I36" t="n">
         <v>6.850000000000001</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="K36" t="n">
@@ -8895,13 +8907,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8928,7 +8940,7 @@
       <c r="I37" t="n">
         <v>7.23</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="K37" t="n">
@@ -8941,13 +8953,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43047</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8974,7 +8986,7 @@
       <c r="I38" t="n">
         <v>7.779999999999999</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43047</v>
       </c>
       <c r="K38" t="n">
@@ -8987,13 +8999,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9020,7 +9032,7 @@
       <c r="I39" t="n">
         <v>6.409999999999999</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="K39" t="n">
@@ -9033,13 +9045,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9066,7 +9078,7 @@
       <c r="I40" t="n">
         <v>7.359999999999999</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K40" t="n">
@@ -9079,13 +9091,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43336</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9112,7 +9124,7 @@
       <c r="I41" t="n">
         <v>7.83</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43336</v>
       </c>
       <c r="K41" t="n">
@@ -9125,13 +9137,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9158,7 +9170,7 @@
       <c r="I42" t="n">
         <v>8.520000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K42" t="n">
@@ -9171,13 +9183,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9204,7 +9216,7 @@
       <c r="I43" t="n">
         <v>10.47</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="K43" t="n">
@@ -9217,13 +9229,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9250,7 +9262,7 @@
       <c r="I44" t="n">
         <v>10.91</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="K44" t="n">
@@ -9263,13 +9275,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43700</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9296,7 +9308,7 @@
       <c r="I45" t="n">
         <v>11.46</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43700</v>
       </c>
       <c r="K45" t="n">
@@ -9309,13 +9321,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9342,7 +9354,7 @@
       <c r="I46" t="n">
         <v>11.27</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="K46" t="n">
@@ -9355,13 +9367,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9388,7 +9400,7 @@
       <c r="I47" t="n">
         <v>10.48</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="K47" t="n">
@@ -9401,13 +9413,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9434,7 +9446,7 @@
       <c r="I48" t="n">
         <v>10.17</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K48" t="n">
@@ -9447,13 +9459,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44069</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9480,7 +9492,7 @@
       <c r="I49" t="n">
         <v>9.27</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44069</v>
       </c>
       <c r="K49" t="n">
@@ -9493,13 +9505,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9526,7 +9538,7 @@
       <c r="I50" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="K50" t="n">
@@ -9539,13 +9551,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9572,7 +9584,7 @@
       <c r="I51" t="n">
         <v>10.98</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="K51" t="n">
@@ -9585,13 +9597,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9618,7 +9630,7 @@
       <c r="I52" t="n">
         <v>11.74</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K52" t="n">
@@ -9631,13 +9643,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44433</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9664,7 +9676,7 @@
       <c r="I53" t="n">
         <v>13.35</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44433</v>
       </c>
       <c r="K53" t="n">
@@ -9677,13 +9689,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9710,7 +9722,7 @@
       <c r="I54" t="n">
         <v>14.33</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K54" t="n">
@@ -9723,13 +9735,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9756,7 +9768,7 @@
       <c r="I55" t="n">
         <v>13.89</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="K55" t="n">
@@ -9769,13 +9781,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9802,7 +9814,7 @@
       <c r="I56" t="n">
         <v>12.97</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="K56" t="n">
@@ -9815,13 +9827,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44797</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9848,7 +9860,7 @@
       <c r="I57" t="n">
         <v>10.09</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44797</v>
       </c>
       <c r="K57" t="n">
@@ -9861,13 +9873,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9894,7 +9906,7 @@
       <c r="I58" t="n">
         <v>9.620000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K58" t="n">
@@ -9907,13 +9919,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9940,7 +9952,7 @@
       <c r="I59" t="n">
         <v>9.69</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="K59" t="n">
@@ -9953,13 +9965,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9986,7 +9998,7 @@
       <c r="I60" t="n">
         <v>11.56</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="K60" t="n">
@@ -9999,13 +10011,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45162</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10032,7 +10044,7 @@
       <c r="I61" t="n">
         <v>16.04</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45162</v>
       </c>
       <c r="K61" t="n">
@@ -10045,13 +10057,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10078,7 +10090,7 @@
       <c r="I62" t="n">
         <v>18.05</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="K62" t="n">
@@ -10091,13 +10103,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45328</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10124,7 +10136,7 @@
       <c r="I63" t="n">
         <v>20.24</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45328</v>
       </c>
       <c r="K63" t="n">
@@ -10137,13 +10149,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10170,7 +10182,7 @@
       <c r="I64" t="n">
         <v>21.26</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="K64" t="n">
@@ -10183,13 +10195,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45526</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10216,7 +10228,7 @@
       <c r="I65" t="n">
         <v>21.84</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45526</v>
       </c>
       <c r="K65" t="n">
@@ -10229,13 +10241,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10262,7 +10274,7 @@
       <c r="I66" t="n">
         <v>22.19</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="K66" t="n">
@@ -10275,13 +10287,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10308,7 +10320,7 @@
       <c r="I67" t="n">
         <v>24.21</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="K67" t="n">
@@ -10321,13 +10333,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10354,7 +10366,7 @@
       <c r="I68" t="n">
         <v>26.02</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="K68" t="n">
@@ -10367,13 +10379,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10400,7 +10412,7 @@
       <c r="I69" t="n">
         <v>27.12</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="K69" t="n">
@@ -10413,13 +10425,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10446,7 +10458,7 @@
       <c r="I70" t="n">
         <v>28.07</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="K70" t="n">
@@ -10459,13 +10471,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10492,7 +10504,7 @@
       <c r="I71" t="n">
         <v>27.42</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K71" t="n">
@@ -10505,13 +10517,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10538,7 +10550,7 @@
       <c r="I72" t="n">
         <v>27.11</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K72" t="n">
@@ -10551,13 +10563,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10584,7 +10596,7 @@
       <c r="I73" t="n">
         <v>28.48</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="K73" t="n">
@@ -10621,52 +10633,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="C2" t="n">
@@ -10695,10 +10707,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40213</v>
       </c>
       <c r="C3" t="n">
@@ -10727,10 +10739,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="C4" t="n">
@@ -10759,10 +10771,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="C5" t="n">
@@ -10791,10 +10803,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C6" t="n">
@@ -10823,10 +10835,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40582</v>
       </c>
       <c r="C7" t="n">
@@ -10855,10 +10867,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C8" t="n">
@@ -10887,10 +10899,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40781</v>
       </c>
       <c r="C9" t="n">
@@ -10919,10 +10931,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="C10" t="n">
@@ -10951,10 +10963,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40947</v>
       </c>
       <c r="C11" t="n">
@@ -10983,10 +10995,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="C12" t="n">
@@ -11015,10 +11027,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41145</v>
       </c>
       <c r="C13" t="n">
@@ -11047,10 +11059,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C14" t="n">
@@ -11079,10 +11091,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41311</v>
       </c>
       <c r="C15" t="n">
@@ -11111,10 +11123,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="C16" t="n">
@@ -11143,10 +11155,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41515</v>
       </c>
       <c r="C17" t="n">
@@ -11175,10 +11187,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="C18" t="n">
@@ -11207,10 +11219,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="C19" t="n">
@@ -11239,10 +11251,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="C20" t="n">
@@ -11271,10 +11283,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41873</v>
       </c>
       <c r="C21" t="n">
@@ -11303,10 +11315,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="C22" t="n">
@@ -11335,10 +11347,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="C23" t="n">
@@ -11367,10 +11379,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="C24" t="n">
@@ -11399,10 +11411,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42242</v>
       </c>
       <c r="C25" t="n">
@@ -11431,10 +11443,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="C26" t="n">
@@ -11463,10 +11475,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="C27" t="n">
@@ -11495,10 +11507,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C28" t="n">
@@ -11527,10 +11539,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42608</v>
       </c>
       <c r="C29" t="n">
@@ -11559,10 +11571,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C30" t="n">
@@ -11591,10 +11603,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="C31" t="n">
@@ -11623,10 +11635,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="C32" t="n">
@@ -11655,10 +11667,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="C33" t="n">
@@ -11687,10 +11699,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43047</v>
       </c>
       <c r="C34" t="n">
@@ -11719,10 +11731,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="C35" t="n">
@@ -11751,10 +11763,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C36" t="n">
@@ -11783,10 +11795,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43336</v>
       </c>
       <c r="C37" t="n">
@@ -11815,10 +11827,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="C38" t="n">
@@ -11847,10 +11859,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="C39" t="n">
@@ -11879,10 +11891,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="C40" t="n">
@@ -11911,10 +11923,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43700</v>
       </c>
       <c r="C41" t="n">
@@ -11943,10 +11955,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C42" t="n">
@@ -11975,10 +11987,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="C43" t="n">
@@ -12007,10 +12019,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C44" t="n">
@@ -12039,10 +12051,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44069</v>
       </c>
       <c r="C45" t="n">
@@ -12071,10 +12083,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="C46" t="n">
@@ -12103,10 +12115,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="C47" t="n">
@@ -12135,10 +12147,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C48" t="n">
@@ -12167,10 +12179,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44433</v>
       </c>
       <c r="C49" t="n">
@@ -12199,10 +12211,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C50" t="n">
@@ -12231,10 +12243,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="C51" t="n">
@@ -12263,10 +12275,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="C52" t="n">
@@ -12295,10 +12307,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44797</v>
       </c>
       <c r="C53" t="n">
@@ -12327,10 +12339,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C54" t="n">
@@ -12359,10 +12371,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="C55" t="n">
@@ -12391,10 +12403,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="C56" t="n">
@@ -12423,10 +12435,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45162</v>
       </c>
       <c r="C57" t="n">
@@ -12455,10 +12467,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="C58" t="n">
@@ -12487,10 +12499,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45328</v>
       </c>
       <c r="C59" t="n">
@@ -12519,10 +12531,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="C60" t="n">
@@ -12551,10 +12563,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45526</v>
       </c>
       <c r="C61" t="n">
@@ -12583,10 +12595,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="C62" t="n">
@@ -12615,10 +12627,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="C63" t="n">
@@ -12647,10 +12659,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="C64" t="n">
@@ -12679,10 +12691,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="C65" t="n">
@@ -12711,10 +12723,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="C66" t="n">
@@ -12743,10 +12755,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="C67" t="n">
@@ -12775,10 +12787,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C68" t="n">
@@ -12807,10 +12819,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="C69" t="n">
@@ -12857,12 +12869,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PH.xlsx
+++ b/salidas/empresas/PH.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>35.9957160949707</v>
+        <v>35.99570465087891</v>
       </c>
       <c r="C2" t="n">
         <v>50.51333236694336</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>38.40908813476562</v>
+        <v>38.40911483764648</v>
       </c>
       <c r="C4" t="n">
         <v>53.7400016784668</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>38.61875915527344</v>
+        <v>38.6187629699707</v>
       </c>
       <c r="C5" t="n">
         <v>54.03333282470703</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>37.27933120727539</v>
+        <v>37.27931976318359</v>
       </c>
       <c r="C6" t="n">
         <v>52.01333236694336</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>37.07863616943359</v>
+        <v>37.07864761352539</v>
       </c>
       <c r="C7" t="n">
         <v>51.73333358764648</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.51753616333008</v>
+        <v>34.51752853393555</v>
       </c>
       <c r="C8" t="n">
         <v>48.15999984741211</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.50568008422852</v>
+        <v>35.50569915771484</v>
       </c>
       <c r="C9" t="n">
         <v>49.36666870117188</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>37.27018737792969</v>
+        <v>37.27017974853516</v>
       </c>
       <c r="C10" t="n">
         <v>51.81999969482422</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>40.09912490844727</v>
+        <v>40.09913635253906</v>
       </c>
       <c r="C11" t="n">
         <v>55.75333404541016</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>40.15095901489258</v>
+        <v>40.15096282958984</v>
       </c>
       <c r="C12" t="n">
         <v>55.6533317565918</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>39.80467987060547</v>
+        <v>39.80466079711914</v>
       </c>
       <c r="C14" t="n">
         <v>55.17333221435547</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>39.74140167236328</v>
+        <v>39.74141311645508</v>
       </c>
       <c r="C15" t="n">
         <v>54.91333389282227</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>41.64235687255859</v>
+        <v>41.64236450195312</v>
       </c>
       <c r="C16" t="n">
         <v>57.54000091552734</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>44.45518493652344</v>
+        <v>44.45517730712891</v>
       </c>
       <c r="C17" t="n">
         <v>61.42666625976562</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>49.03703689575195</v>
+        <v>49.03701782226562</v>
       </c>
       <c r="C18" t="n">
         <v>67.57333374023438</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>47.36794281005859</v>
+        <v>47.36793518066406</v>
       </c>
       <c r="C19" t="n">
         <v>65.27333068847656</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>47.74047088623047</v>
+        <v>47.7404670715332</v>
       </c>
       <c r="C20" t="n">
         <v>65.78666687011719</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>52.15170288085938</v>
+        <v>52.15169906616211</v>
       </c>
       <c r="C21" t="n">
         <v>71.64666748046875</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>58.50144577026367</v>
+        <v>58.50140762329102</v>
       </c>
       <c r="C23" t="n">
         <v>80.37000274658203</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>57.97005081176758</v>
+        <v>57.97001266479492</v>
       </c>
       <c r="C24" t="n">
         <v>79.43000030517578</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>54.963134765625</v>
+        <v>54.96315383911133</v>
       </c>
       <c r="C25" t="n">
         <v>75.30999755859375</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>50.7166862487793</v>
+        <v>50.71669387817383</v>
       </c>
       <c r="C28" t="n">
         <v>69.26999664306641</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>58.46296691894531</v>
+        <v>58.46293258666992</v>
       </c>
       <c r="C29" t="n">
         <v>79.84999847412109</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>62.14601516723633</v>
+        <v>62.14598846435547</v>
       </c>
       <c r="C30" t="n">
         <v>84.66999816894531</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>52.34737396240234</v>
+        <v>52.34738159179688</v>
       </c>
       <c r="C31" t="n">
         <v>71.31999969482422</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>45.27182388305664</v>
+        <v>45.27181243896484</v>
       </c>
       <c r="C32" t="n">
         <v>61.68000030517578</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>47.21604537963867</v>
+        <v>47.21606063842773</v>
       </c>
       <c r="C33" t="n">
         <v>64.06999969482422</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>39.05807495117188</v>
+        <v>39.05807113647461</v>
       </c>
       <c r="C34" t="n">
         <v>53</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>28.57135009765625</v>
+        <v>28.57135200500488</v>
       </c>
       <c r="C35" t="n">
         <v>38.77000045776367</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>30.49230194091797</v>
+        <v>30.4923038482666</v>
       </c>
       <c r="C36" t="n">
         <v>41.08000183105469</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>31.57601928710938</v>
+        <v>31.57601356506348</v>
       </c>
       <c r="C37" t="n">
         <v>42.54000091552734</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>28.36200141906738</v>
+        <v>28.36201477050781</v>
       </c>
       <c r="C38" t="n">
         <v>38.20999908447266</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>25.37813568115234</v>
+        <v>25.37814712524414</v>
       </c>
       <c r="C40" t="n">
         <v>33.97999954223633</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>33.86988067626953</v>
+        <v>33.8698844909668</v>
       </c>
       <c r="C41" t="n">
         <v>45.34999847412109</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>31.73619842529297</v>
+        <v>31.73620414733887</v>
       </c>
       <c r="C42" t="n">
         <v>42.2599983215332</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>32.26188659667969</v>
+        <v>32.26188278198242</v>
       </c>
       <c r="C43" t="n">
         <v>42.95999908447266</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>33.253173828125</v>
+        <v>33.25316619873047</v>
       </c>
       <c r="C44" t="n">
         <v>44.27999877929688</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>36.73223495483398</v>
+        <v>36.73225021362305</v>
       </c>
       <c r="C45" t="n">
         <v>48.65999984741211</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>39.13276290893555</v>
+        <v>39.13275527954102</v>
       </c>
       <c r="C46" t="n">
         <v>51.84000015258789</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>39.97823333740234</v>
+        <v>39.97822189331055</v>
       </c>
       <c r="C47" t="n">
         <v>52.95999908447266</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>40.91268157958984</v>
+        <v>40.91266632080078</v>
       </c>
       <c r="C48" t="n">
         <v>53.95999908447266</v>
@@ -1397,7 +1397,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>40.85202026367188</v>
+        <v>40.85200500488281</v>
       </c>
       <c r="C49" t="n">
         <v>53.88000106811523</v>
@@ -1422,7 +1422,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>42.39115905761719</v>
+        <v>42.39117050170898</v>
       </c>
       <c r="C50" t="n">
         <v>55.90999984741211</v>
@@ -1447,7 +1447,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>45.93201446533203</v>
+        <v>45.9320182800293</v>
       </c>
       <c r="C51" t="n">
         <v>60.31000137329102</v>
@@ -1497,7 +1497,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>52.68739318847656</v>
+        <v>52.6873779296875</v>
       </c>
       <c r="C53" t="n">
         <v>69.18000030517578</v>
@@ -1547,7 +1547,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>42.40464782714844</v>
+        <v>42.40462112426758</v>
       </c>
       <c r="C55" t="n">
         <v>55.45999908447266</v>
@@ -1597,7 +1597,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>45.41983413696289</v>
+        <v>45.41982269287109</v>
       </c>
       <c r="C57" t="n">
         <v>59.15999984741211</v>
@@ -1655,7 +1655,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>58.77093124389648</v>
+        <v>58.77092742919922</v>
       </c>
       <c r="C59" t="n">
         <v>76.55000305175781</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>61.81571578979492</v>
+        <v>61.81570816040039</v>
       </c>
       <c r="C60" t="n">
         <v>80.23000335693359</v>
@@ -1713,7 +1713,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>66.49251556396484</v>
+        <v>66.49250793457031</v>
       </c>
       <c r="C61" t="n">
         <v>86.30000305175781</v>
@@ -1742,7 +1742,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>68.88871002197266</v>
+        <v>68.88872528076172</v>
       </c>
       <c r="C62" t="n">
         <v>89.41000366210938</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>73.20459747314453</v>
+        <v>73.20457458496094</v>
       </c>
       <c r="C64" t="n">
         <v>94.68000030517578</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>72.92623901367188</v>
+        <v>72.92621612548828</v>
       </c>
       <c r="C65" t="n">
         <v>94.31999969482422</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>68.98334503173828</v>
+        <v>68.98333740234375</v>
       </c>
       <c r="C66" t="n">
         <v>88.84999847412109</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>69.67431640625</v>
+        <v>69.67435455322266</v>
       </c>
       <c r="C67" t="n">
         <v>89.73999786376953</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>61.35130310058594</v>
+        <v>61.35129547119141</v>
       </c>
       <c r="C68" t="n">
         <v>79.01999664306641</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>57.32381439208984</v>
+        <v>57.32381820678711</v>
       </c>
       <c r="C69" t="n">
         <v>73.43000030517578</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>63.66273880004883</v>
+        <v>63.66277313232422</v>
       </c>
       <c r="C71" t="n">
         <v>81.55000305175781</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>64.91249084472656</v>
+        <v>64.9124755859375</v>
       </c>
       <c r="C72" t="n">
         <v>82.77999877929688</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>59.79194641113281</v>
+        <v>59.79192733764648</v>
       </c>
       <c r="C73" t="n">
         <v>76.25</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>70.739501953125</v>
+        <v>70.73951721191406</v>
       </c>
       <c r="C75" t="n">
         <v>89.80999755859375</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>69.06969451904297</v>
+        <v>69.06967163085938</v>
       </c>
       <c r="C77" t="n">
         <v>87.69000244140625</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>64.69625091552734</v>
+        <v>64.69624328613281</v>
       </c>
       <c r="C78" t="n">
         <v>81.73999786376953</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>60.84960174560547</v>
+        <v>60.84960556030273</v>
       </c>
       <c r="C79" t="n">
         <v>76.87999725341797</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>63.57234191894531</v>
+        <v>63.57232284545898</v>
       </c>
       <c r="C80" t="n">
         <v>80.31999969482422</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>63.62228012084961</v>
+        <v>63.62227249145508</v>
       </c>
       <c r="C81" t="n">
         <v>79.98000335693359</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>66.48602294921875</v>
+        <v>66.48599243164062</v>
       </c>
       <c r="C82" t="n">
         <v>83.58000183105469</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>62.57223129272461</v>
+        <v>62.57224655151367</v>
       </c>
       <c r="C83" t="n">
         <v>78.66000366210938</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>65.68334197998047</v>
+        <v>65.68329620361328</v>
       </c>
       <c r="C84" t="n">
         <v>82.15000152587891</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>68.01000213623047</v>
+        <v>68.01003265380859</v>
       </c>
       <c r="C85" t="n">
         <v>85.05999755859375</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>74.33448791503906</v>
+        <v>74.33450317382812</v>
       </c>
       <c r="C86" t="n">
         <v>92.97000122070312</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>73.55979156494141</v>
+        <v>73.55977630615234</v>
       </c>
       <c r="C88" t="n">
         <v>91.58000183105469</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>71.14206695556641</v>
+        <v>71.14208984375</v>
       </c>
       <c r="C89" t="n">
         <v>88.56999969482422</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>80.51924133300781</v>
+        <v>80.51920318603516</v>
       </c>
       <c r="C90" t="n">
         <v>99.76000213623047</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>77.00016021728516</v>
+        <v>77.00013732910156</v>
       </c>
       <c r="C91" t="n">
         <v>95.40000152587891</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>83.36032867431641</v>
+        <v>83.36034393310547</v>
       </c>
       <c r="C92" t="n">
         <v>103.2799987792969</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>81.02420043945312</v>
+        <v>81.02418518066406</v>
       </c>
       <c r="C93" t="n">
         <v>99.94999694824219</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>88.13358306884766</v>
+        <v>88.13359069824219</v>
       </c>
       <c r="C94" t="n">
         <v>108.7200012207031</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>94.61874389648438</v>
+        <v>94.61873626708984</v>
       </c>
       <c r="C95" t="n">
         <v>116.7200012207031</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>95.89887237548828</v>
+        <v>95.89886474609375</v>
       </c>
       <c r="C96" t="n">
         <v>117.8399963378906</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>104.6879806518555</v>
+        <v>104.6880035400391</v>
       </c>
       <c r="C97" t="n">
         <v>128.6399993896484</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>92.26118469238281</v>
+        <v>92.26119232177734</v>
       </c>
       <c r="C98" t="n">
         <v>113.370002746582</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>98.52423858642578</v>
+        <v>98.52423095703125</v>
       </c>
       <c r="C99" t="n">
         <v>120.5500030517578</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>103.6976623535156</v>
+        <v>103.6976776123047</v>
       </c>
       <c r="C101" t="n">
         <v>126.879997253418</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>102.7488250732422</v>
+        <v>102.7488098144531</v>
       </c>
       <c r="C102" t="n">
         <v>125.2300033569336</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>103.1590423583984</v>
+        <v>103.159049987793</v>
       </c>
       <c r="C103" t="n">
         <v>125.7300033569336</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>94.31426239013672</v>
+        <v>94.31425476074219</v>
       </c>
       <c r="C104" t="n">
         <v>114.9499969482422</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>95.15584564208984</v>
+        <v>95.15582275390625</v>
       </c>
       <c r="C105" t="n">
         <v>115.5</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>104.6549606323242</v>
+        <v>104.6549301147461</v>
       </c>
       <c r="C107" t="n">
         <v>127.0299987792969</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>106.7631683349609</v>
+        <v>106.7631301879883</v>
       </c>
       <c r="C109" t="n">
         <v>128.9499969482422</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>96.42216491699219</v>
+        <v>96.42214202880859</v>
       </c>
       <c r="C110" t="n">
         <v>116.4599990844727</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>98.86058044433594</v>
+        <v>98.86056518554688</v>
       </c>
       <c r="C112" t="n">
         <v>118.7799987792969</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>99.34331512451172</v>
+        <v>99.34329223632812</v>
       </c>
       <c r="C113" t="n">
         <v>119.3600006103516</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>100.7532043457031</v>
+        <v>100.7532119750977</v>
       </c>
       <c r="C114" t="n">
         <v>120.4300003051758</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>97.3231201171875</v>
+        <v>97.32311248779297</v>
       </c>
       <c r="C115" t="n">
         <v>116.3300018310547</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>94.32803344726562</v>
+        <v>94.32804870605469</v>
       </c>
       <c r="C116" t="n">
         <v>112.75</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>90.6383056640625</v>
+        <v>90.63829803466797</v>
       </c>
       <c r="C117" t="n">
         <v>107.6600036621094</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>81.91627502441406</v>
+        <v>81.91629028320312</v>
       </c>
       <c r="C118" t="n">
         <v>97.30000305175781</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>88.14630126953125</v>
+        <v>88.14627075195312</v>
       </c>
       <c r="C119" t="n">
         <v>104.6999969482422</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>82.13417053222656</v>
+        <v>82.13416290283203</v>
       </c>
       <c r="C121" t="n">
         <v>96.98000335693359</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>82.28660583496094</v>
+        <v>82.28659057617188</v>
       </c>
       <c r="C122" t="n">
         <v>97.16000366210938</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>94.66324615478516</v>
+        <v>94.66322326660156</v>
       </c>
       <c r="C124" t="n">
         <v>111.0800018310547</v>
@@ -3569,7 +3569,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>98.87315368652344</v>
+        <v>98.87312316894531</v>
       </c>
       <c r="C125" t="n">
         <v>116.0199966430664</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>98.42137145996094</v>
+        <v>98.42135620117188</v>
       </c>
       <c r="C126" t="n">
         <v>114.8399963378906</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>92.60212707519531</v>
+        <v>92.6021728515625</v>
       </c>
       <c r="C127" t="n">
         <v>108.0500030517578</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>97.86433410644531</v>
+        <v>97.86431884765625</v>
       </c>
       <c r="C128" t="n">
         <v>114.1900024414062</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>105.5511779785156</v>
+        <v>105.5511703491211</v>
       </c>
       <c r="C129" t="n">
         <v>122.5299987792969</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>105.7406997680664</v>
+        <v>105.7406845092773</v>
       </c>
       <c r="C131" t="n">
         <v>122.75</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>120.2816925048828</v>
+        <v>120.2817306518555</v>
       </c>
       <c r="C132" t="n">
         <v>138.9299926757812</v>
@@ -3801,7 +3801,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>121.2080917358398</v>
+        <v>121.2081451416016</v>
       </c>
       <c r="C133" t="n">
         <v>140</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>127.3810882568359</v>
+        <v>127.3810653686523</v>
       </c>
       <c r="C134" t="n">
         <v>147.1300048828125</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>139.4224700927734</v>
+        <v>139.4224548339844</v>
       </c>
       <c r="C136" t="n">
         <v>160.3200073242188</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>139.8399047851562</v>
+        <v>139.8398895263672</v>
       </c>
       <c r="C137" t="n">
         <v>160.8000030517578</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>137.5140686035156</v>
+        <v>137.5140075683594</v>
       </c>
       <c r="C138" t="n">
         <v>157.4700012207031</v>
@@ -3975,7 +3975,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>139.5662384033203</v>
+        <v>139.5662689208984</v>
       </c>
       <c r="C139" t="n">
         <v>159.8200073242188</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>144.9456024169922</v>
+        <v>144.9455871582031</v>
       </c>
       <c r="C140" t="n">
         <v>165.9799957275391</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>153.48291015625</v>
+        <v>153.4828948974609</v>
       </c>
       <c r="C142" t="n">
         <v>175.0200042724609</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>160.1389007568359</v>
+        <v>160.138916015625</v>
       </c>
       <c r="C143" t="n">
         <v>182.6100006103516</v>
@@ -4120,7 +4120,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>165.0075225830078</v>
+        <v>165.0075073242188</v>
       </c>
       <c r="C144" t="n">
         <v>187.4900054931641</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>175.6477813720703</v>
+        <v>175.6477508544922</v>
       </c>
       <c r="C145" t="n">
         <v>199.5800018310547</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>177.26708984375</v>
+        <v>177.2670593261719</v>
       </c>
       <c r="C146" t="n">
         <v>201.4199981689453</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>157.6367034912109</v>
+        <v>157.6366882324219</v>
       </c>
       <c r="C147" t="n">
         <v>178.4700012207031</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>151.0651702880859</v>
+        <v>151.0651550292969</v>
       </c>
       <c r="C148" t="n">
         <v>171.0299987792969</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>145.4033813476562</v>
+        <v>145.4034271240234</v>
       </c>
       <c r="C149" t="n">
         <v>164.6199951171875</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>151.6237945556641</v>
+        <v>151.6237487792969</v>
       </c>
       <c r="C150" t="n">
         <v>170.8999938964844</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>138.2713012695312</v>
+        <v>138.2713165283203</v>
       </c>
       <c r="C151" t="n">
         <v>155.8500061035156</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>149.9824676513672</v>
+        <v>149.9824829101562</v>
       </c>
       <c r="C152" t="n">
         <v>169.0500030517578</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>156.4869995117188</v>
+        <v>156.4869537353516</v>
       </c>
       <c r="C153" t="n">
         <v>175.6000061035156</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>163.9103240966797</v>
+        <v>163.9103546142578</v>
       </c>
       <c r="C154" t="n">
         <v>183.9299926757812</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>135.1259918212891</v>
+        <v>135.1260375976562</v>
       </c>
       <c r="C155" t="n">
         <v>151.6300048828125</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>153.9987945556641</v>
+        <v>153.9988098144531</v>
       </c>
       <c r="C156" t="n">
         <v>172.0399932861328</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>133.5002288818359</v>
+        <v>133.5002746582031</v>
       </c>
       <c r="C157" t="n">
         <v>149.1399993896484</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>147.5269927978516</v>
+        <v>147.5270233154297</v>
       </c>
       <c r="C158" t="n">
         <v>164.8099975585938</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>154.3294067382812</v>
+        <v>154.3294219970703</v>
       </c>
       <c r="C160" t="n">
         <v>171.6199951171875</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>162.8363647460938</v>
+        <v>162.8363494873047</v>
       </c>
       <c r="C161" t="n">
         <v>181.0800018310547</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>137.6784820556641</v>
+        <v>137.6785125732422</v>
       </c>
       <c r="C162" t="n">
         <v>152.3200073242188</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>153.6680908203125</v>
+        <v>153.6680297851562</v>
       </c>
       <c r="C163" t="n">
         <v>170.0099945068359</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>150.6719055175781</v>
+        <v>150.6718597412109</v>
       </c>
       <c r="C165" t="n">
         <v>165.7700042724609</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>164.1602478027344</v>
+        <v>164.1602783203125</v>
       </c>
       <c r="C166" t="n">
         <v>180.6100006103516</v>
@@ -4787,7 +4787,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>166.7779388427734</v>
+        <v>166.7779846191406</v>
       </c>
       <c r="C167" t="n">
         <v>183.4900054931641</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>178.6560821533203</v>
+        <v>178.6561279296875</v>
       </c>
       <c r="C170" t="n">
         <v>195.6900024414062</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>169.39501953125</v>
+        <v>169.3950347900391</v>
       </c>
       <c r="C171" t="n">
         <v>184.7700042724609</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>118.9349517822266</v>
+        <v>118.9349746704102</v>
       </c>
       <c r="C172" t="n">
         <v>129.7299957275391</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>165.9466400146484</v>
+        <v>165.9467163085938</v>
       </c>
       <c r="C174" t="n">
         <v>179.9700012207031</v>
@@ -5019,7 +5019,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>168.9895629882812</v>
+        <v>168.9895324707031</v>
       </c>
       <c r="C175" t="n">
         <v>183.2700042724609</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>164.9784698486328</v>
+        <v>164.9784240722656</v>
       </c>
       <c r="C176" t="n">
         <v>178.9199981689453</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>190.7578735351562</v>
+        <v>190.7577972412109</v>
       </c>
       <c r="C177" t="n">
         <v>206.0099945068359</v>
@@ -5106,7 +5106,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>187.3595123291016</v>
+        <v>187.3594818115234</v>
       </c>
       <c r="C178" t="n">
         <v>202.3399963378906</v>
@@ -5135,7 +5135,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>192.933837890625</v>
+        <v>192.9338226318359</v>
       </c>
       <c r="C179" t="n">
         <v>208.3600006103516</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>248.4764099121094</v>
+        <v>248.4763946533203</v>
       </c>
       <c r="C180" t="n">
         <v>267.260009765625</v>
@@ -5193,7 +5193,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>253.264404296875</v>
+        <v>253.2644195556641</v>
       </c>
       <c r="C181" t="n">
         <v>272.4100036621094</v>
@@ -5251,7 +5251,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>267.6371154785156</v>
+        <v>267.6370849609375</v>
       </c>
       <c r="C183" t="n">
         <v>286.9599914550781</v>
@@ -5280,7 +5280,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>294.1901245117188</v>
+        <v>294.1900024414062</v>
       </c>
       <c r="C184" t="n">
         <v>315.4299926757812</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>292.6791381835938</v>
+        <v>292.6790771484375</v>
       </c>
       <c r="C185" t="n">
         <v>313.8099975585938</v>
@@ -5338,7 +5338,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>288.3409729003906</v>
+        <v>288.3409423828125</v>
       </c>
       <c r="C186" t="n">
         <v>308.1499938964844</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>287.3677062988281</v>
+        <v>287.3678283691406</v>
       </c>
       <c r="C187" t="n">
         <v>307.1099853515625</v>
@@ -5425,7 +5425,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>278.5442199707031</v>
+        <v>278.5442504882812</v>
       </c>
       <c r="C189" t="n">
         <v>296.6700134277344</v>
@@ -5454,7 +5454,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>262.5358581542969</v>
+        <v>262.5359497070312</v>
       </c>
       <c r="C190" t="n">
         <v>279.6199951171875</v>
@@ -5483,7 +5483,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>278.4691162109375</v>
+        <v>278.4691467285156</v>
       </c>
       <c r="C191" t="n">
         <v>296.5899963378906</v>
@@ -5512,7 +5512,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>284.4940795898438</v>
+        <v>284.4940185546875</v>
       </c>
       <c r="C192" t="n">
         <v>302.0599975585938</v>
@@ -5570,7 +5570,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>291.9816589355469</v>
+        <v>291.9817199707031</v>
       </c>
       <c r="C194" t="n">
         <v>310.010009765625</v>
@@ -5599,7 +5599,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>280.0717163085938</v>
+        <v>280.0718078613281</v>
       </c>
       <c r="C195" t="n">
         <v>296.3900146484375</v>
@@ -5628,7 +5628,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>268.1371765136719</v>
+        <v>268.1371459960938</v>
       </c>
       <c r="C196" t="n">
         <v>283.760009765625</v>
@@ -5715,7 +5715,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>233.6766204833984</v>
+        <v>233.6765899658203</v>
       </c>
       <c r="C199" t="n">
         <v>246.0500030517578</v>
@@ -5744,7 +5744,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>274.5521850585938</v>
+        <v>274.55224609375</v>
       </c>
       <c r="C200" t="n">
         <v>289.0899963378906</v>
@@ -5831,7 +5831,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>277.2664794921875</v>
+        <v>277.2665710449219</v>
       </c>
       <c r="C203" t="n">
         <v>290.6199951171875</v>
@@ -5860,7 +5860,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>286.5217590332031</v>
+        <v>286.5218200683594</v>
       </c>
       <c r="C204" t="n">
         <v>298.9400024414062</v>
@@ -5947,7 +5947,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>338.5130004882812</v>
+        <v>338.5129089355469</v>
       </c>
       <c r="C207" t="n">
         <v>351.8500061035156</v>
@@ -6034,7 +6034,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>309.6956481933594</v>
+        <v>309.6957702636719</v>
       </c>
       <c r="C210" t="n">
         <v>320.4400024414062</v>
@@ -6092,7 +6092,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>396.2625122070312</v>
+        <v>396.262451171875</v>
       </c>
       <c r="C212" t="n">
         <v>410.010009765625</v>
@@ -6121,7 +6121,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>404.424072265625</v>
+        <v>404.4241027832031</v>
       </c>
       <c r="C213" t="n">
         <v>416.8999938964844</v>
@@ -6150,7 +6150,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>377.8634948730469</v>
+        <v>377.8633728027344</v>
       </c>
       <c r="C214" t="n">
         <v>389.5199890136719</v>
@@ -6179,7 +6179,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>357.8702087402344</v>
+        <v>357.8701782226562</v>
       </c>
       <c r="C215" t="n">
         <v>368.9100036621094</v>
@@ -6208,7 +6208,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>421.7288208007812</v>
+        <v>421.7287902832031</v>
       </c>
       <c r="C216" t="n">
         <v>433.1799926757812</v>
@@ -6266,7 +6266,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>452.2208557128906</v>
+        <v>452.220947265625</v>
       </c>
       <c r="C218" t="n">
         <v>464.5</v>
@@ -6353,7 +6353,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>532.0365600585938</v>
+        <v>532.036376953125</v>
       </c>
       <c r="C221" t="n">
         <v>544.9099731445312</v>
@@ -6382,7 +6382,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>520.49169921875</v>
+        <v>520.4918212890625</v>
       </c>
       <c r="C222" t="n">
         <v>531.52001953125</v>
@@ -6469,7 +6469,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>589.3748168945312</v>
+        <v>589.374755859375</v>
       </c>
       <c r="C225" t="n">
         <v>600.2000122070312</v>
@@ -6585,7 +6585,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>626.0379028320312</v>
+        <v>626.0379638671875</v>
       </c>
       <c r="C229" t="n">
         <v>636.030029296875</v>
@@ -6672,7 +6672,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>599.714111328125</v>
+        <v>599.7140502929688</v>
       </c>
       <c r="C232" t="n">
         <v>607.8499755859375</v>
@@ -6701,7 +6701,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>596.9613037109375</v>
+        <v>596.96142578125</v>
       </c>
       <c r="C233" t="n">
         <v>605.0599975585938</v>
@@ -6730,7 +6730,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>657.6484985351562</v>
+        <v>657.6484375</v>
       </c>
       <c r="C234" t="n">
         <v>664.7000122070312</v>
@@ -6788,7 +6788,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>724.1356811523438</v>
+        <v>724.1356201171875</v>
       </c>
       <c r="C236" t="n">
         <v>731.9000244140625</v>
@@ -6817,7 +6817,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>751.2943115234375</v>
+        <v>751.2943725585938</v>
       </c>
       <c r="C237" t="n">
         <v>759.3499755859375</v>
@@ -6904,7 +6904,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>856.4324340820312</v>
+        <v>856.4324951171875</v>
       </c>
       <c r="C240" t="n">
         <v>861.7000122070312</v>
@@ -7020,7 +7020,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>891.4257202148438</v>
+        <v>891.4256591796875</v>
       </c>
       <c r="C244" t="n">
         <v>895.239990234375</v>
@@ -7049,7 +7049,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>905.5452880859375</v>
+        <v>905.5452270507812</v>
       </c>
       <c r="C245" t="n">
         <v>909.4199829101562</v>
